--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="77">
   <si>
     <t>_id</t>
   </si>
@@ -263,6 +263,18 @@
   </si>
   <si>
     <t>7,8,9</t>
+  </si>
+  <si>
+    <t>红色珍品材料</t>
+  </si>
+  <si>
+    <t>8,8</t>
+  </si>
+  <si>
+    <t>12,13</t>
+  </si>
+  <si>
+    <t>红色珍品材料自选包</t>
   </si>
   <si>
     <t>战士技能全选</t>
@@ -1924,7 +1936,39 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:13">
-      <c r="H21" s="1"/>
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="3:13">
       <c r="H22" s="1"/>
@@ -1934,7 +1978,7 @@
         <v>101</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E23" s="1">
         <v>5</v>
@@ -1949,10 +1993,10 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>48</v>
@@ -1961,7 +2005,7 @@
         <v>9999</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:13">
@@ -1969,7 +2013,7 @@
         <v>102</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E24" s="1">
         <v>5</v>
@@ -1984,10 +2028,10 @@
         <v>2</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>48</v>
@@ -1996,7 +2040,7 @@
         <v>9999</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
@@ -2004,7 +2048,7 @@
         <v>103</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E25" s="1">
         <v>5</v>
@@ -2019,10 +2063,10 @@
         <v>2</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>48</v>
@@ -2031,7 +2075,7 @@
         <v>9999</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
@@ -2416,7 +2460,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2431,16 +2475,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="87">
   <si>
     <t>_id</t>
   </si>
@@ -305,6 +305,36 @@
   </si>
   <si>
     <t>道士1-7阶技能各1本</t>
+  </si>
+  <si>
+    <t>红宠自选</t>
+  </si>
+  <si>
+    <t>8,8,8</t>
+  </si>
+  <si>
+    <t>202,203,204</t>
+  </si>
+  <si>
+    <t>战士红宠</t>
+  </si>
+  <si>
+    <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>101,104,107,110,201,204,207,210,301,304,307,310</t>
+  </si>
+  <si>
+    <t>法师红宠</t>
+  </si>
+  <si>
+    <t>102,105,108,111,202,205,208,211,302,305,308,311</t>
+  </si>
+  <si>
+    <t>道士红宠</t>
+  </si>
+  <si>
+    <t>103,106,109,112,203,206,209,212,303,306,309,312</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -2085,13 +2115,132 @@
       <c r="H27" s="1"/>
     </row>
     <row r="28" customHeight="1" spans="3:13">
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1"/>
-    <row r="30" s="1" customFormat="1" customHeight="1"/>
+      <c r="C28" s="1">
+        <v>201</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="1">
+        <v>6</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C29" s="1">
+        <v>202</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C30" s="1">
+        <v>203</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="1">
+        <v>6</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
     <row r="31" customHeight="1" spans="3:13">
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
+      <c r="C31" s="1">
+        <v>204</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="1">
+        <v>6</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="32" customHeight="1" spans="3:13">
       <c r="H32" s="1"/>
@@ -2460,7 +2609,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2475,16 +2624,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="88">
   <si>
     <t>_id</t>
   </si>
@@ -319,22 +319,25 @@
     <t>战士红宠</t>
   </si>
   <si>
-    <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
-  </si>
-  <si>
-    <t>101,104,107,110,201,204,207,210,301,304,307,310</t>
+    <t>21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>101,104,107,110,201,204,207,210</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>法师红宠</t>
   </si>
   <si>
-    <t>102,105,108,111,202,205,208,211,302,305,308,311</t>
+    <t>102,105,108,111,202,205,208,211</t>
   </si>
   <si>
     <t>道士红宠</t>
   </si>
   <si>
-    <t>103,106,109,112,203,206,209,212,303,306,309,312</t>
+    <t>103,106,109,112,203,206,209,212</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -2172,10 +2175,10 @@
         <v>77</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -2183,7 +2186,7 @@
         <v>203</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
@@ -2201,13 +2204,13 @@
         <v>76</v>
       </c>
       <c r="J30" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:13">
@@ -2215,7 +2218,7 @@
         <v>204</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
@@ -2233,13 +2236,13 @@
         <v>76</v>
       </c>
       <c r="J31" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="M31" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:13">
@@ -2609,7 +2612,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2624,16 +2627,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -319,25 +319,25 @@
     <t>战士红宠</t>
   </si>
   <si>
-    <t>21,21,21,21,21,21,21,21,21</t>
-  </si>
-  <si>
-    <t>101,104,107,110,201,204,207,210</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
+    <t>21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>101,104,107,110,113,201,204,207,210,213</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>法师红宠</t>
   </si>
   <si>
-    <t>102,105,108,111,202,205,208,211</t>
+    <t>102,105,108,111,114,202,205,208,211,214</t>
   </si>
   <si>
     <t>道士红宠</t>
   </si>
   <si>
-    <t>103,106,109,112,203,206,209,212</t>
+    <t>103,106,109,112,115,203,206,209,212,215</t>
   </si>
   <si>
     <t>金色刺杀自选</t>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -319,25 +319,25 @@
     <t>战士红宠</t>
   </si>
   <si>
-    <t>21,21,21,21,21,21,21,21,21,21</t>
-  </si>
-  <si>
-    <t>101,104,107,110,113,201,204,207,210,213</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+    <t>21,21,21,21,21,21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>101,104,107,110,113,201,204,207,210,213,301,304,307,310,313</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>法师红宠</t>
   </si>
   <si>
-    <t>102,105,108,111,114,202,205,208,211,214</t>
+    <t>102,105,108,111,114,202,205,208,211,214,302,305,308,311,314</t>
   </si>
   <si>
     <t>道士红宠</t>
   </si>
   <si>
-    <t>103,106,109,112,115,203,206,209,212,215</t>
+    <t>103,106,109,112,115,203,206,209,212,215,303,306,309,312,315</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
